--- a/数据/无人机应急物资运输基础数据/调度中心与服务区.xlsx
+++ b/数据/无人机应急物资运输基础数据/调度中心与服务区.xlsx
@@ -5,15 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SF_Dir\第二十三届中国研究生数学建模竞赛 - 中文题目\中文题目\D题\数据\无人机应急物资运输基础数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HH\Desktop\(南航学习资料汇总)博四下结束暑假\赛题+参考答案 - 最终版本\赛题+参考答案 - 最终版本\赛题\数据\无人机应急物资运输基础数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="调度中心" sheetId="1" r:id="rId1"/>
-    <sheet name="服务区" sheetId="2" r:id="rId2"/>
+    <sheet name="数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调度中心</t>
+    </r>
+  </si>
   <si>
     <r>
       <rPr>
@@ -143,6 +153,17 @@
         <charset val="134"/>
       </rPr>
       <t>凤丹村无人机调度中心</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务区</t>
     </r>
   </si>
   <si>
@@ -346,7 +367,7 @@
     <numFmt numFmtId="176" formatCode="0.0000000"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -358,8 +379,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -370,6 +392,11 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -518,6 +545,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -825,159 +858,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -988,15 +1025,11 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1469,526 +1502,396 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13" style="7" customWidth="1"/>
-    <col min="2" max="2" width="24" style="7" customWidth="1"/>
-    <col min="3" max="4" width="14" style="7" customWidth="1"/>
-    <col min="5" max="5" width="12" style="7" customWidth="1"/>
-    <col min="6" max="6" width="21.4" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.4" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:6">
-      <c r="A2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:6">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4">
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6">
         <v>109.2308517</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D3" s="6">
         <v>23.0085095</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E3" s="7">
         <v>127.7</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:6">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:6">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+    <row r="5" ht="24" customHeight="1" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6">
+        <v>109.2432319</v>
+      </c>
+      <c r="D7" s="6">
+        <v>23.0335927</v>
+      </c>
+      <c r="E7" s="7">
+        <v>154</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2100</v>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6">
+        <v>109.2585519</v>
+      </c>
+      <c r="D8" s="6">
+        <v>23.0703271</v>
+      </c>
+      <c r="E8" s="7">
+        <v>189.5</v>
+      </c>
+      <c r="F8" s="9">
+        <v>330</v>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6">
+        <v>109.1688578</v>
+      </c>
+      <c r="D9" s="6">
+        <v>23.0402714</v>
+      </c>
+      <c r="E9" s="7">
+        <v>308.5</v>
+      </c>
+      <c r="F9" s="9">
+        <v>275</v>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="6">
+        <v>109.2381714</v>
+      </c>
+      <c r="D10" s="6">
+        <v>23.0778414</v>
+      </c>
+      <c r="E10" s="7">
+        <v>198.3</v>
+      </c>
+      <c r="F10" s="9">
+        <v>188</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6">
+        <v>109.2283003</v>
+      </c>
+      <c r="D11" s="6">
+        <v>23.0561338</v>
+      </c>
+      <c r="E11" s="7">
+        <v>165</v>
+      </c>
+      <c r="F11" s="9">
+        <v>126</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="6">
+        <v>109.1997836</v>
+      </c>
+      <c r="D12" s="6">
+        <v>23.007714</v>
+      </c>
+      <c r="E12" s="7">
+        <v>284.8</v>
+      </c>
+      <c r="F12" s="9">
+        <v>121</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6">
+        <v>109.1928191</v>
+      </c>
+      <c r="D13" s="6">
+        <v>23.0294186</v>
+      </c>
+      <c r="E13" s="7">
+        <v>318.5</v>
+      </c>
+      <c r="F13" s="9">
+        <v>76</v>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="6">
+        <v>109.2127472</v>
+      </c>
+      <c r="D14" s="6">
+        <v>23.0795113</v>
+      </c>
+      <c r="E14" s="7">
+        <v>240.9</v>
+      </c>
+      <c r="F14" s="9">
+        <v>55</v>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="6">
+        <v>109.2541424</v>
+      </c>
+      <c r="D15" s="6">
+        <v>23.0552989</v>
+      </c>
+      <c r="E15" s="7">
+        <v>200</v>
+      </c>
+      <c r="F15" s="9">
+        <v>45</v>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="6">
+        <v>109.2760168</v>
+      </c>
+      <c r="D16" s="6">
+        <v>23.0194009</v>
+      </c>
+      <c r="E16" s="7">
+        <v>321.6</v>
+      </c>
+      <c r="F16" s="9">
+        <v>31</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="A17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="6">
+        <v>109.2203356</v>
+      </c>
+      <c r="D17" s="6">
+        <v>23.0319231</v>
+      </c>
+      <c r="E17" s="7">
+        <v>182.1</v>
+      </c>
+      <c r="F17" s="9">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="6">
+        <v>109.2831357</v>
+      </c>
+      <c r="D18" s="6">
+        <v>23.054464</v>
+      </c>
+      <c r="E18" s="7">
+        <v>249.8</v>
+      </c>
+      <c r="F18" s="9">
+        <v>16</v>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="A19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="6">
+        <v>109.2713839</v>
+      </c>
+      <c r="D19" s="6">
+        <v>23.0310882</v>
+      </c>
+      <c r="E19" s="7">
+        <v>321.7</v>
+      </c>
+      <c r="F19" s="9">
+        <v>14</v>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="A20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="6">
+        <v>109.2835966</v>
+      </c>
+      <c r="D20" s="6">
+        <v>23.0052097</v>
+      </c>
+      <c r="E20" s="7">
+        <v>321</v>
+      </c>
+      <c r="F20" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="6">
+        <v>109.1923786</v>
+      </c>
+      <c r="D21" s="6">
+        <v>23.0494548</v>
+      </c>
+      <c r="E21" s="7">
+        <v>444.5</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="5"/>
-  <cols>
-    <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="12.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="12.4166666666667" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4">
-        <v>109.2432319</v>
-      </c>
-      <c r="D2" s="4">
-        <v>23.0335927</v>
-      </c>
-      <c r="E2" s="5">
-        <v>154</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4">
-        <v>109.2585519</v>
-      </c>
-      <c r="D3" s="4">
-        <v>23.0703271</v>
-      </c>
-      <c r="E3" s="5">
-        <v>189.5</v>
-      </c>
-      <c r="F3" s="6">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4">
-        <v>109.1688578</v>
-      </c>
-      <c r="D4" s="4">
-        <v>23.0402714</v>
-      </c>
-      <c r="E4" s="5">
-        <v>308.5</v>
-      </c>
-      <c r="F4" s="6">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="4">
-        <v>109.2381714</v>
-      </c>
-      <c r="D5" s="4">
-        <v>23.0778414</v>
-      </c>
-      <c r="E5" s="5">
-        <v>198.3</v>
-      </c>
-      <c r="F5" s="6">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4">
-        <v>109.2283003</v>
-      </c>
-      <c r="D6" s="4">
-        <v>23.0561338</v>
-      </c>
-      <c r="E6" s="5">
-        <v>165</v>
-      </c>
-      <c r="F6" s="6">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4">
-        <v>109.1997836</v>
-      </c>
-      <c r="D7" s="4">
-        <v>23.007714</v>
-      </c>
-      <c r="E7" s="5">
-        <v>284.8</v>
-      </c>
-      <c r="F7" s="6">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4">
-        <v>109.1928191</v>
-      </c>
-      <c r="D8" s="4">
-        <v>23.0294186</v>
-      </c>
-      <c r="E8" s="5">
-        <v>318.5</v>
-      </c>
-      <c r="F8" s="6">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4">
-        <v>109.2127472</v>
-      </c>
-      <c r="D9" s="4">
-        <v>23.0795113</v>
-      </c>
-      <c r="E9" s="5">
-        <v>240.9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="4">
-        <v>109.2541424</v>
-      </c>
-      <c r="D10" s="4">
-        <v>23.0552989</v>
-      </c>
-      <c r="E10" s="5">
-        <v>200</v>
-      </c>
-      <c r="F10" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="4">
-        <v>109.2760168</v>
-      </c>
-      <c r="D11" s="4">
-        <v>23.0194009</v>
-      </c>
-      <c r="E11" s="5">
-        <v>321.6</v>
-      </c>
-      <c r="F11" s="6">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="4">
-        <v>109.2203356</v>
-      </c>
-      <c r="D12" s="4">
-        <v>23.0319231</v>
-      </c>
-      <c r="E12" s="5">
-        <v>182.1</v>
-      </c>
-      <c r="F12" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="4">
-        <v>109.2831357</v>
-      </c>
-      <c r="D13" s="4">
-        <v>23.054464</v>
-      </c>
-      <c r="E13" s="5">
-        <v>249.8</v>
-      </c>
-      <c r="F13" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="4">
-        <v>109.2713839</v>
-      </c>
-      <c r="D14" s="4">
-        <v>23.0310882</v>
-      </c>
-      <c r="E14" s="5">
-        <v>321.7</v>
-      </c>
-      <c r="F14" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="4">
-        <v>109.2835966</v>
-      </c>
-      <c r="D15" s="4">
-        <v>23.0052097</v>
-      </c>
-      <c r="E15" s="5">
-        <v>321</v>
-      </c>
-      <c r="F15" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="4">
-        <v>109.1923786</v>
-      </c>
-      <c r="D16" s="4">
-        <v>23.0494548</v>
-      </c>
-      <c r="E16" s="5">
-        <v>444.5</v>
-      </c>
-      <c r="F16" s="6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>